--- a/Insurance Rate Data Scraper/output/ga_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/ga_final_rates.xlsx
@@ -3575,7 +3575,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3585,10 +3585,14 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4071,7 +4075,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4081,10 +4085,14 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4782,7 +4790,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4792,10 +4800,14 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -27442,7 +27454,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S268" t="inlineStr">
@@ -27452,10 +27464,14 @@
       </c>
       <c r="T268" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U268" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -28830,7 +28846,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S282" t="inlineStr">
@@ -28840,10 +28856,14 @@
       </c>
       <c r="T282" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U282" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -28926,7 +28946,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S283" t="inlineStr">
@@ -28936,10 +28956,14 @@
       </c>
       <c r="T283" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U283" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -29022,7 +29046,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S284" t="inlineStr">
@@ -29032,10 +29056,14 @@
       </c>
       <c r="T284" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U284" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -29118,7 +29146,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
@@ -29128,10 +29156,14 @@
       </c>
       <c r="T285" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U285" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -30402,7 +30434,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S298" t="inlineStr">
@@ -30412,10 +30444,14 @@
       </c>
       <c r="T298" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U298" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -30498,7 +30534,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S299" t="inlineStr">
@@ -30508,10 +30544,14 @@
       </c>
       <c r="T299" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U299" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -30594,7 +30634,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S300" t="inlineStr">
@@ -30604,10 +30644,14 @@
       </c>
       <c r="T300" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U300" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -30690,7 +30734,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S301" t="inlineStr">
@@ -30700,10 +30744,14 @@
       </c>
       <c r="T301" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U301" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -30786,7 +30834,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S302" t="inlineStr">
@@ -30796,10 +30844,14 @@
       </c>
       <c r="T302" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U302" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -30882,7 +30934,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S303" t="inlineStr">
@@ -30892,10 +30944,14 @@
       </c>
       <c r="T303" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U303" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -30978,7 +31034,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S304" t="inlineStr">
@@ -30988,10 +31044,14 @@
       </c>
       <c r="T304" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U304" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -31074,7 +31134,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S305" t="inlineStr">
@@ -31084,10 +31144,14 @@
       </c>
       <c r="T305" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U305" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -31170,7 +31234,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S306" t="inlineStr">
@@ -31180,10 +31244,14 @@
       </c>
       <c r="T306" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U306" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -31266,7 +31334,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S307" t="inlineStr">
@@ -31276,10 +31344,14 @@
       </c>
       <c r="T307" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U307" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -31362,7 +31434,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S308" t="inlineStr">
@@ -31372,10 +31444,14 @@
       </c>
       <c r="T308" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U308" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -31458,7 +31534,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S309" t="inlineStr">
@@ -31468,10 +31544,14 @@
       </c>
       <c r="T309" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U309" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -40105,7 +40185,7 @@
       </c>
       <c r="R394" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S394" t="inlineStr">
@@ -40115,10 +40195,14 @@
       </c>
       <c r="T394" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U394" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -40201,7 +40285,7 @@
       </c>
       <c r="R395" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S395" t="inlineStr">
@@ -40211,10 +40295,14 @@
       </c>
       <c r="T395" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U395" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -40297,7 +40385,7 @@
       </c>
       <c r="R396" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S396" t="inlineStr">
@@ -40307,10 +40395,14 @@
       </c>
       <c r="T396" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U396" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -40393,7 +40485,7 @@
       </c>
       <c r="R397" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S397" t="inlineStr">
@@ -40403,10 +40495,14 @@
       </c>
       <c r="T397" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U397" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -40489,7 +40585,7 @@
       </c>
       <c r="R398" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S398" t="inlineStr">
@@ -40499,10 +40595,14 @@
       </c>
       <c r="T398" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U398" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">

--- a/Insurance Rate Data Scraper/output/ga_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/ga_final_rates.xlsx
@@ -36927,7 +36927,7 @@
       </c>
       <c r="R362" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S362" t="inlineStr">
@@ -36937,10 +36937,14 @@
       </c>
       <c r="T362" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U362" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -37129,7 +37133,7 @@
       </c>
       <c r="R364" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S364" t="inlineStr">
@@ -37139,10 +37143,14 @@
       </c>
       <c r="T364" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U364" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -37331,7 +37339,7 @@
       </c>
       <c r="R366" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S366" t="inlineStr">
@@ -37341,10 +37349,14 @@
       </c>
       <c r="T366" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U366" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -37634,7 +37646,7 @@
       </c>
       <c r="R369" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S369" t="inlineStr">
@@ -37644,10 +37656,14 @@
       </c>
       <c r="T369" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U369" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -37836,7 +37852,7 @@
       </c>
       <c r="R371" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S371" t="inlineStr">
@@ -37846,10 +37862,14 @@
       </c>
       <c r="T371" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U371" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -38038,7 +38058,7 @@
       </c>
       <c r="R373" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S373" t="inlineStr">
@@ -38048,10 +38068,14 @@
       </c>
       <c r="T373" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U373" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -38139,7 +38163,7 @@
       </c>
       <c r="R374" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S374" t="inlineStr">
@@ -38149,10 +38173,14 @@
       </c>
       <c r="T374" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U374" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -38240,7 +38268,7 @@
       </c>
       <c r="R375" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S375" t="inlineStr">
@@ -38250,10 +38278,14 @@
       </c>
       <c r="T375" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U375" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -38341,7 +38373,7 @@
       </c>
       <c r="R376" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S376" t="inlineStr">
@@ -38351,10 +38383,14 @@
       </c>
       <c r="T376" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U376" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -38442,7 +38478,7 @@
       </c>
       <c r="R377" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S377" t="inlineStr">
@@ -38452,10 +38488,14 @@
       </c>
       <c r="T377" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U377" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">

--- a/Insurance Rate Data Scraper/output/ga_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/ga_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U481"/>
+  <dimension ref="A1:U486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,7 +622,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -723,7 +722,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -824,7 +822,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -925,7 +922,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1026,7 +1022,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1127,7 +1122,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1228,7 +1222,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1329,7 +1322,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1430,7 +1422,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1531,7 +1522,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1942,7 +1932,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4908,7 +4897,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5009,7 +4997,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5110,7 +5097,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5211,7 +5197,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5312,7 +5297,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5413,7 +5397,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5514,7 +5497,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5615,7 +5597,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5716,7 +5697,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5817,7 +5797,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6338,7 +6317,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6649,7 +6627,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6750,7 +6727,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6851,7 +6827,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6952,7 +6927,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7053,7 +7027,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7154,7 +7127,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7255,7 +7227,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7356,7 +7327,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7457,7 +7427,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7558,7 +7527,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7654,7 +7622,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7750,7 +7717,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7846,7 +7812,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7947,7 +7912,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8048,7 +8012,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8149,7 +8112,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8250,7 +8212,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8351,7 +8312,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8452,7 +8412,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8553,7 +8512,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8654,7 +8612,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8755,7 +8712,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8856,7 +8812,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8957,7 +8912,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9583,7 +9537,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9684,7 +9637,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9785,7 +9737,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -10201,7 +10152,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10407,7 +10357,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10508,7 +10457,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10814,7 +10762,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10910,7 +10857,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -11006,7 +10952,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11102,7 +11047,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -11298,7 +11242,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11394,7 +11337,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11490,7 +11432,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11586,7 +11527,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11682,7 +11622,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11778,7 +11717,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11874,7 +11812,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11970,7 +11907,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -12066,7 +12002,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -12162,7 +12097,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12258,7 +12192,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -14059,7 +13992,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -14160,7 +14092,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -14261,7 +14192,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -14362,7 +14292,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -14778,7 +14707,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -14879,7 +14807,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -14980,7 +14907,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -15081,7 +15007,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -15182,7 +15107,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -15283,7 +15207,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -15384,7 +15307,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -15485,7 +15407,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -15586,7 +15507,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -15687,7 +15607,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -15998,7 +15917,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -16099,7 +16017,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -16190,7 +16107,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -16281,7 +16197,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -16372,7 +16287,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -16463,7 +16377,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -16554,7 +16467,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -16645,7 +16557,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -16736,7 +16647,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -16827,7 +16737,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -16918,7 +16827,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -17009,7 +16917,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -19000,7 +18907,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -19101,7 +19007,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -19202,7 +19107,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -19303,7 +19207,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -19404,7 +19307,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -19505,7 +19407,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -19606,7 +19507,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -19707,7 +19607,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -19808,7 +19707,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -19909,7 +19807,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -20010,7 +19907,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -20216,7 +20112,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -20317,7 +20212,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -20418,7 +20312,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -20519,7 +20412,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -20620,7 +20512,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -20721,7 +20612,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -20822,7 +20712,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -21028,7 +20917,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -21129,7 +21017,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -21545,7 +21432,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -21646,7 +21532,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -21747,7 +21632,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -21848,7 +21732,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -21949,7 +21832,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -22050,7 +21932,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -22151,7 +22032,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -22252,7 +22132,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -22353,7 +22232,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -22454,7 +22332,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -22660,7 +22537,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -22761,7 +22637,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -22967,7 +22842,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -23803,7 +23677,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -23904,7 +23777,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -24005,7 +23877,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -24106,7 +23977,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -24207,7 +24077,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -24308,7 +24177,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -24409,7 +24277,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -24510,7 +24377,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -24716,7 +24582,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -24817,7 +24682,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -25118,7 +24982,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -25209,7 +25072,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -25300,7 +25162,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -25391,7 +25252,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -25482,7 +25342,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -25573,7 +25432,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -25664,7 +25522,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -25755,7 +25612,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -25846,7 +25702,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -25937,7 +25792,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -26353,7 +26207,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -26454,7 +26307,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -27280,7 +27132,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -27376,7 +27227,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -27667,7 +27517,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -27763,7 +27612,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -27859,7 +27707,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -27955,7 +27802,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -28056,7 +27902,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -28157,7 +28002,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -28258,7 +28102,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -28359,7 +28202,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -28460,7 +28302,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -28561,7 +28402,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -28662,7 +28502,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -28763,7 +28602,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -29679,7 +29517,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -29775,7 +29612,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -29871,7 +29707,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -29967,7 +29802,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -30063,7 +29897,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -30159,7 +29992,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -30255,7 +30087,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -30351,7 +30182,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -31652,7 +31482,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -31963,7 +31792,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -32064,7 +31892,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -32270,7 +32097,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -32686,7 +32512,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -32787,7 +32612,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -32888,7 +32712,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -33094,7 +32917,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -33300,7 +33122,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -33611,7 +33432,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -33712,7 +33532,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -33908,7 +33727,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -34004,7 +33822,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -34105,7 +33922,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -34311,7 +34127,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -35022,7 +34837,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -35123,7 +34937,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -35224,7 +35037,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -35320,7 +35132,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -35416,7 +35227,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -35512,7 +35322,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -35608,7 +35417,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -35704,7 +35512,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -36435,7 +36242,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -36536,7 +36342,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -36637,7 +36442,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -36738,7 +36542,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -36839,7 +36642,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -37045,7 +36847,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -37251,7 +37052,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -37457,7 +37257,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -37558,7 +37357,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -37764,7 +37562,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -37970,7 +37767,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -38596,7 +38392,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -38907,7 +38702,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -39318,7 +39112,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -39419,7 +39212,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -39520,7 +39312,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -39621,7 +39412,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -39722,7 +39512,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -40743,7 +40532,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -40844,7 +40632,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -40945,7 +40732,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -41046,7 +40832,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -41147,7 +40932,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -41248,7 +41032,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -41349,7 +41132,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -41450,7 +41232,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -41551,7 +41332,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -41652,7 +41432,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -42278,7 +42057,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -42379,7 +42157,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -42480,7 +42257,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -42581,7 +42357,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -42682,7 +42457,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -42783,7 +42557,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -42884,7 +42657,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -42985,7 +42757,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -43086,7 +42857,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -43187,7 +42957,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -43288,7 +43057,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -43389,7 +43157,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -43490,7 +43257,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -43591,7 +43357,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -43692,7 +43457,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -43893,7 +43657,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -44309,7 +44072,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -44410,7 +44172,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -44511,7 +44272,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -44612,7 +44372,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -44818,7 +44577,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -44919,7 +44677,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -45115,7 +44872,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -45311,7 +45067,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -45407,7 +45162,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -45503,7 +45257,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -45599,7 +45352,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -46095,7 +45847,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -46376,7 +46127,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -46687,7 +46437,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -46788,7 +46537,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -46889,7 +46637,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -47190,7 +46937,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -47291,7 +47037,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -47392,7 +47137,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -47488,7 +47232,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -47584,7 +47327,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -47680,7 +47422,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -48096,7 +47837,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -48197,7 +47937,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -48503,7 +48242,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -48599,7 +48337,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -48695,7 +48432,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -48796,7 +48532,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -48897,7 +48632,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -48998,7 +48732,465 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>07/24/2025</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>12.461%</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I482" t="n">
+        <v>14823</v>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>48935728</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>1697.200%</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>-69.600%</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>CFPC-134508132</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134508132/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>09/21/2025</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>12.461%</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>3.614%</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>2319926</t>
+        </is>
+      </c>
+      <c r="I483" t="n">
+        <v>14823</v>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>64194422</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>1684.000%</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>-73.600%</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>CFPC-134294144</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134294144/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>02/18/2024</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>39.590%</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>18.711%</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>3860999</t>
+        </is>
+      </c>
+      <c r="I484" t="n">
+        <v>5263</v>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>20635159</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>1384.500%</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>4.800%</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>CFPC-133859077</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>2023-11-06</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/133859077/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T484" t="inlineStr">
+        <is>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>CFPC-134290937</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134290937/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T485" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>COUNTRY Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>CFPC-134290937</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134290937/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T486" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Insurance Rate Data Scraper/output/ga_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/ga_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U555"/>
+  <dimension ref="A1:U616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55411,6 +55411,5797 @@
       </c>
       <c r="U555" t="inlineStr"/>
     </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>09/23/2026</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I556" t="n">
+        <v>49031</v>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>140342484</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>21.600%</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>-17.300%</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>SFMA-134828206</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="Q556" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134828206/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R556" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S556" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T556" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>09/23/2026</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I557" t="n">
+        <v>2011295</v>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>3434004743</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>18.500%</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>-17.400%</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>SFMA-134828206</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="Q557" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134828206/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R557" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S557" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T557" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>10.500%</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>6.100%</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>85174065</t>
+        </is>
+      </c>
+      <c r="I558" t="n">
+        <v>878925</v>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>1402715547</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>28.300%</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>-31.000%</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>SFMA-134927479</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>Pending Company Response</t>
+        </is>
+      </c>
+      <c r="Q558" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134927479/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R558" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S558" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T558" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>09/20/2026</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>GEICO Casualty Company</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I559" t="n">
+        <v>0</v>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>GECC-134941345</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q559" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134941345/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R559" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S559" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T559" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>09/20/2026</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>GEICO Secure Insurance Company</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I560" t="n">
+        <v>0</v>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>GECC-134941345</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q560" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134941345/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R560" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S560" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T560" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>GEICO Choice Insurance Company</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>4.500%</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>4.500%</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>460257</t>
+        </is>
+      </c>
+      <c r="I561" t="n">
+        <v>6299</v>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>10227932</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>13.760%</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>-2.950%</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>GECC-135009901</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="Q561" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/135009901/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R561" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S561" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T561" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>GEICO Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>2.300%</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>2.300%</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>112865</t>
+        </is>
+      </c>
+      <c r="I562" t="n">
+        <v>2986</v>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>4907181</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>11.880%</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>-5.220%</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>GECC-135009901</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="Q562" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/135009901/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R562" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S562" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T562" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>GEICO Advantage Insurance Company</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>1.700%</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>1.700%</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>212110</t>
+        </is>
+      </c>
+      <c r="I563" t="n">
+        <v>9680</v>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>12477044</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>12.390%</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>-8.230%</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>GECC-135009901</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="Q563" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/135009901/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R563" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S563" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T563" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>GEICO Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>4.100%</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>4.100%</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>876774</t>
+        </is>
+      </c>
+      <c r="I564" t="n">
+        <v>14306</v>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>21384724</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>14.420%</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>-3.040%</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>GECC-135009901</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="Q564" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/135009901/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R564" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S564" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T564" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Progressive Advanced Insurance Company</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I565" t="n">
+        <v>832</v>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>3666769</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>PRGS-134913531</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q565" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134913531/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R565" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S565" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T565" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Progressive American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I566" t="n">
+        <v>1394</v>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>5714237</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>PRGS-134913531</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q566" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134913531/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R566" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S566" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T566" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Progressive Choice Insurance Company</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I567" t="n">
+        <v>182011</v>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>578770351</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>PRGS-134913531</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q567" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134913531/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R567" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S567" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T567" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I568" t="n">
+        <v>513</v>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>2827758</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>PRGS-134913531</t>
+        </is>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q568" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134913531/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R568" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S568" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T568" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Progressive Freedom Insurance Company</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I569" t="n">
+        <v>106235</v>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>367444481</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>PRGS-134913531</t>
+        </is>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q569" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134913531/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R569" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S569" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T569" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Progressive Premier Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I570" t="n">
+        <v>467956</v>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>1340432645</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>PRGS-134913531</t>
+        </is>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q570" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134913531/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R570" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S570" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T570" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Progressive Southeastern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I571" t="n">
+        <v>1429</v>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>4773170</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>PRGS-134913531</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q571" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134913531/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R571" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S571" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T571" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Progressive Mountain Insurance Company</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I572" t="n">
+        <v>373751</v>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>1152070138</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>PRGS-134913531</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q572" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134913531/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R572" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S572" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T572" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>07/13/2026</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>1.100%</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>1.100%</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>1655533</t>
+        </is>
+      </c>
+      <c r="I573" t="n">
+        <v>36024</v>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>150502991</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>6.600%</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>-5.600%</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>ALSE-134945918</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="Q573" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134945918/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R573" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S573" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T573" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>07/13/2026</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Allstate Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>24.400%</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>6.500%</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>93584</t>
+        </is>
+      </c>
+      <c r="I574" t="n">
+        <v>434</v>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>1439753</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>8.400%</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>ALSE-134946171</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q574" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134946171/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R574" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S574" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T574" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>07/13/2026</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Allstate Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>5.500%</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>5.500%</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>116632</t>
+        </is>
+      </c>
+      <c r="I575" t="n">
+        <v>434</v>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>2120576</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>8.300%</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>ALSE-134945888</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q575" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134945888/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R575" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S575" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T575" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>10/13/2026</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I576" t="n">
+        <v>11751</v>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>26322240</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>1.500%</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>-3.000%</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>ALSE-134921023</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>Exam</t>
+        </is>
+      </c>
+      <c r="Q576" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134921023/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R576" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S576" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T576" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>08/18/2026</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I577" t="n">
+        <v>89629</v>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>336258466</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>-12.000%</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>ALSE-134920240</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>Exam</t>
+        </is>
+      </c>
+      <c r="Q577" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134920240/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R577" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S577" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T577" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>07/13/2026</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Allstate Northbrook Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>14.800%</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>11.800%</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>579773</t>
+        </is>
+      </c>
+      <c r="I578" t="n">
+        <v>763</v>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>4913334</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>19.300%</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>ALSE-134946594</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q578" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134946594/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R578" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S578" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T578" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>07/13/2026</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Allstate Northbrook Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>22.700%</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>12.300%</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>398900</t>
+        </is>
+      </c>
+      <c r="I579" t="n">
+        <v>763</v>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>3243088</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>14.700%</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>ALSE-134946663</t>
+        </is>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q579" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134946663/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R579" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S579" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T579" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>08/23/2026</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I580" t="n">
+        <v>133969</v>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>374959834</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>25.700%</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>-36.600%</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>TRVD-G134929097</t>
+        </is>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>Exam</t>
+        </is>
+      </c>
+      <c r="Q580" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134935686/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R580" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S580" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T580" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Travelers Property Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>-24.000%</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>-10.100%</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>-40758973</t>
+        </is>
+      </c>
+      <c r="I581" t="n">
+        <v>109120</v>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>403554184</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>-12.500%</t>
+        </is>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>TRVD-G134911970</t>
+        </is>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q581" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134915738/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R581" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S581" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T581" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>08/31/2026</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>5.900%</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>3.300%</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>3557</t>
+        </is>
+      </c>
+      <c r="I582" t="n">
+        <v>11</v>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>108898</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>5.100%</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>1.500%</t>
+        </is>
+      </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>LBPM-134985970</t>
+        </is>
+      </c>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q582" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134985970/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R582" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S582" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T582" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>08/31/2026</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>5.900%</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>3.100%</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>310532</t>
+        </is>
+      </c>
+      <c r="I583" t="n">
+        <v>1786</v>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>9891938</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>5.900%</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>-3.600%</t>
+        </is>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>LBPM-134985970</t>
+        </is>
+      </c>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q583" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134985970/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R583" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S583" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T583" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>07/20/2026</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>The First Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I584" t="n">
+        <v>0</v>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>LBPM-134952411</t>
+        </is>
+      </c>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q584" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134952411/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R584" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S584" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T584" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U584" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>07/20/2026</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I585" t="n">
+        <v>0</v>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>LBPM-134952411</t>
+        </is>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q585" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134952411/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R585" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S585" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T585" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>The First Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>5.900%</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>4.100%</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>658668</t>
+        </is>
+      </c>
+      <c r="I586" t="n">
+        <v>3758</v>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>16207371</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>12.300%</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>-3.300%</t>
+        </is>
+      </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>LBPM-134991339</t>
+        </is>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q586" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134991339/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R586" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S586" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T586" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>5.900%</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>3.800%</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>2163586</t>
+        </is>
+      </c>
+      <c r="I587" t="n">
+        <v>13685</v>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>56463226</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>12.500%</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>-4.000%</t>
+        </is>
+      </c>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>LBPM-134991339</t>
+        </is>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q587" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134991339/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R587" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S587" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T587" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U587" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I588" t="n">
+        <v>0</v>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>4684622</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>LBPM-134936299</t>
+        </is>
+      </c>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>Exam</t>
+        </is>
+      </c>
+      <c r="Q588" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134936299/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R588" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S588" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T588" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I589" t="n">
+        <v>0</v>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>10688699</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>LBPM-134936299</t>
+        </is>
+      </c>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>Exam</t>
+        </is>
+      </c>
+      <c r="Q589" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134936299/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R589" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S589" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T589" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>-0.250%</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>-1509</t>
+        </is>
+      </c>
+      <c r="I590" t="n">
+        <v>164</v>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>606503</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>2.500%</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>-15.000%</t>
+        </is>
+      </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>LBPM-135011027</t>
+        </is>
+      </c>
+      <c r="Q590" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/135011027/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R590" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S590" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T590" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>-0.050%</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>-6931</t>
+        </is>
+      </c>
+      <c r="I591" t="n">
+        <v>5532</v>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>13917162</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>11.100%</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>-19.000%</t>
+        </is>
+      </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>LBPM-135011027</t>
+        </is>
+      </c>
+      <c r="Q591" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/135011027/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R591" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S591" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T591" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Indiana</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>5.600%</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>3.700%</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>771875</t>
+        </is>
+      </c>
+      <c r="I592" t="n">
+        <v>4748</v>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>20712416</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>7.700%</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>-3.100%</t>
+        </is>
+      </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>LBPM-134911822</t>
+        </is>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q592" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134911822/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R592" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S592" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T592" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>5.600%</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>3.400%</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>1478972</t>
+        </is>
+      </c>
+      <c r="I593" t="n">
+        <v>11642</v>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>43787370</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>7.800%</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>-3.300%</t>
+        </is>
+      </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>LBPM-134911822</t>
+        </is>
+      </c>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q593" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134911822/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R593" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S593" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T593" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U593" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Oregon</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I594" t="n">
+        <v>0</v>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>64303711</t>
+        </is>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>LBPM-134919744</t>
+        </is>
+      </c>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>Exam</t>
+        </is>
+      </c>
+      <c r="Q594" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134919744/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R594" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S594" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T594" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>09/19/2026</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Safeco National Insurance Company</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I595" t="n">
+        <v>4049</v>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>1789251</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t>LBPM-135000372</t>
+        </is>
+      </c>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="Q595" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/135000372/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R595" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S595" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T595" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U595" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>05/28/2026</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>American States Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>5.600%</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>3.500%</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>337988</t>
+        </is>
+      </c>
+      <c r="I596" t="n">
+        <v>2907</v>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>9622069</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>7.900%</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>-0.700%</t>
+        </is>
+      </c>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>LBPM-134911767</t>
+        </is>
+      </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="Q596" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134911767/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R596" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S596" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T596" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Encompass Insurance Company</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I597" t="n">
+        <v>0</v>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>2941864</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>GMMX-134963332</t>
+        </is>
+      </c>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q597" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134963332/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R597" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S597" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T597" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Farmers Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>04.0002 Mobile Homeowners</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I598" t="n">
+        <v>2266</v>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>3921806</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>FORE-134994818</t>
+        </is>
+      </c>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q598" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134994818/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R598" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S598" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T598" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U598" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Nationwide Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>-186</t>
+        </is>
+      </c>
+      <c r="I599" t="n">
+        <v>4478</v>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>11121849</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>81.700%</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>-41.800%</t>
+        </is>
+      </c>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>NWPP-G134915722</t>
+        </is>
+      </c>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>Exam</t>
+        </is>
+      </c>
+      <c r="Q599" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134924294/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R599" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S599" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T599" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U599" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Nationwide General Insurance Company</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>-135</t>
+        </is>
+      </c>
+      <c r="I600" t="n">
+        <v>15535</v>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>41414681</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>33.700%</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>-18.100%</t>
+        </is>
+      </c>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N600" t="inlineStr">
+        <is>
+          <t>NWPP-G134915722</t>
+        </is>
+      </c>
+      <c r="O600" t="inlineStr">
+        <is>
+          <t>Exam</t>
+        </is>
+      </c>
+      <c r="Q600" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134924294/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R600" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S600" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T600" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Nationwide Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I601" t="n">
+        <v>5242</v>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>15107379</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>24.900%</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>-10.200%</t>
+        </is>
+      </c>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>NWPP-G134915722</t>
+        </is>
+      </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>Exam</t>
+        </is>
+      </c>
+      <c r="Q601" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134924294/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R601" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S601" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T601" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U601" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Nationwide Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>-14</t>
+        </is>
+      </c>
+      <c r="I602" t="n">
+        <v>3695</v>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>11409678</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>6.800%</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>-10.000%</t>
+        </is>
+      </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>NWPP-G134915722</t>
+        </is>
+      </c>
+      <c r="O602" t="inlineStr">
+        <is>
+          <t>Exam</t>
+        </is>
+      </c>
+      <c r="Q602" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134924294/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R602" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S602" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T602" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Nationwide Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>-9.000%</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>-2128609</t>
+        </is>
+      </c>
+      <c r="I603" t="n">
+        <v>7331</v>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>23651211</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>1.600%</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>-19.300%</t>
+        </is>
+      </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>NWPP-G135002597</t>
+        </is>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q603" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/135003636/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R603" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S603" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T603" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U603" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>COUNTRY Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="I604" t="n">
+        <v>58678</v>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>107129061</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>CFPC-134983942</t>
+        </is>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q604" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134983942/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R604" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S604" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T604" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U604" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>0.500%</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>-4368</t>
+        </is>
+      </c>
+      <c r="I605" t="n">
+        <v>8083</v>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>26878742</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>13.100%</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>-10.400%</t>
+        </is>
+      </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>FARM-134937299</t>
+        </is>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q605" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134937299/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R605" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S605" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T605" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U605" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I606" t="n">
+        <v>8083</v>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>26878742</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>FARM-135019633</t>
+        </is>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="Q606" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/135019633/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R606" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S606" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T606" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U606" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Fire Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>1.800%</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>1.700%</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>476000</t>
+        </is>
+      </c>
+      <c r="I607" t="n">
+        <v>26433</v>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>27736000</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>11.700%</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>-4.600%</t>
+        </is>
+      </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N607" t="inlineStr">
+        <is>
+          <t>FARM-134979328</t>
+        </is>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q607" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134979328/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R607" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S607" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T607" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U607" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Garrison Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>-11.800%</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>-4.700%</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>-8119936</t>
+        </is>
+      </c>
+      <c r="I608" t="n">
+        <v>48109</v>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>172764598</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>20.000%</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N608" t="inlineStr">
+        <is>
+          <t>USAA-134985182</t>
+        </is>
+      </c>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="Q608" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134986381/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R608" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S608" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T608" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U608" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>United Services Automobile Association</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>-0.100%</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I609" t="n">
+        <v>101686</v>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>413682548</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>20.000%</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N609" t="inlineStr">
+        <is>
+          <t>USAA-134985182</t>
+        </is>
+      </c>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="Q609" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134986381/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R609" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S609" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T609" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U609" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>USAA Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>12.300%</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>-4.500%</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>-17955666</t>
+        </is>
+      </c>
+      <c r="I610" t="n">
+        <v>104159</v>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>399014791</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>20.000%</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N610" t="inlineStr">
+        <is>
+          <t>USAA-134985182</t>
+        </is>
+      </c>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="Q610" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134986381/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R610" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S610" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T610" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U610" t="inlineStr"/>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>USAA General Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>-6.300%</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>-2.400%</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>-7089905</t>
+        </is>
+      </c>
+      <c r="I611" t="n">
+        <v>81187</v>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>295412701</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>20.000%</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>USAA-134985182</t>
+        </is>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="Q611" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134986381/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R611" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S611" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T611" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U611" t="inlineStr"/>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Garrison Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>6.200%</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>4.600%</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>3740851</t>
+        </is>
+      </c>
+      <c r="I612" t="n">
+        <v>48109</v>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>81419189</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>20.000%</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N612" t="inlineStr">
+        <is>
+          <t>USAA-134985185</t>
+        </is>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q612" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134986388/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R612" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S612" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T612" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U612" t="inlineStr"/>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>United Services Automobile Association</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>37.200%</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>13.800%</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>24239022</t>
+        </is>
+      </c>
+      <c r="I613" t="n">
+        <v>101686</v>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>175394719</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>20.000%</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>USAA-134985185</t>
+        </is>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q613" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134986388/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R613" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S613" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T613" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U613" t="inlineStr"/>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>USAA Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>10.600%</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>8.900%</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>16775385</t>
+        </is>
+      </c>
+      <c r="I614" t="n">
+        <v>104159</v>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>189518205</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>20.000%</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>USAA-134985185</t>
+        </is>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q614" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134986388/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R614" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S614" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T614" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U614" t="inlineStr"/>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>USAA General Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>16.600%</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>9.300%</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>12849717</t>
+        </is>
+      </c>
+      <c r="I615" t="n">
+        <v>81187</v>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>138616333</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>20.000%</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>USAA-134985185</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q615" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/134986388/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R615" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S615" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T615" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U615" t="inlineStr"/>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>MGA Insurance Company, Inc.</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>5.900%</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>-3.700%</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>-2210584</t>
+        </is>
+      </c>
+      <c r="I616" t="n">
+        <v>20851</v>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>58976098</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>9.500%</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>-14.400%</t>
+        </is>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>GNSC-135014638</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q616" t="inlineStr">
+        <is>
+          <t>output/pdfs/GA/135014638/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R616" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S616" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T616" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U616" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
